--- a/mock_question_bank_template_v2.xlsx
+++ b/mock_question_bank_template_v2.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passages" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$K$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,13 +28,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,8 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,66 +428,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Part</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Set ID</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Passage ID</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Local Passage No. (optional)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Question Order</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
@@ -490,48 +512,43 @@
           <t>EVS_MCQ</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>EVS-MCQ-001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Sample EVS question</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sample question</t>
+          <t>Option A</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Option B</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Option C</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Option D</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,158 +561,205 @@
           <t>EVS_PASSAGE</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EVS-P001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Passage question 1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Question 1</t>
+          <t>Option A</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Option B</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Option C</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Option D</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LANGUAGE</t>
+          <t>EVS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LANGUAGE_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>EVS_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Passage question 2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Question 1</t>
+          <t>Option A</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Option B</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Option C</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Option D</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LANGUAGE_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Language question 1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>ARITHMETIC</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ARITHMETIC</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AR-001</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Sample arithmetic question</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Option D</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -708,19 +772,24 @@
   </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Passage ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Local Passage No.</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Passage Title</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Passage</t>
         </is>
@@ -729,34 +798,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EVS-P001</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EVS Passage 1</t>
+          <t>Passage 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paste the full EVS passage here.</t>
+          <t>Paste the full passage here.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Language Passage 1</t>
+          <t>Passage 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paste the full language passage here.</t>
+          <t>Paste the full passage here.</t>
         </is>
       </c>
     </row>

--- a/mock_question_bank_template_v2.xlsx
+++ b/mock_question_bank_template_v2.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passages" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passages" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -428,7 +429,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="115" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MOCK TEST BULK UPLOAD — PASSAGE RULES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1. For EVS_PASSAGE and LANGUAGE_PASSAGE, Local Passage No. is mandatory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2. Exactly 5 question rows must use the same Local Passage No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3. Question Order must be exactly 1, 2, 3, 4, 5 for each passage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4. The Passages sheet must contain exactly one row for each Local Passage No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. Each passage row must contain a Passage Title and the complete Passage text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. The system generates the permanent Passage ID automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7. Do not split one passage across different local passage numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8. Language supports multiple complete 5-question passage groups.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -457,7 +538,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Local Passage No. (optional)</t>
+          <t>Local Passage No. (required for passage parts)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -512,7 +593,6 @@
           <t>EVS_MCQ</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>1</t>
@@ -548,7 +628,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -601,7 +680,6 @@
           <t>B</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -654,7 +732,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -707,7 +784,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -720,7 +796,6 @@
           <t>ARITHMETIC</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
@@ -756,7 +831,536 @@
           <t>D</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EVS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EVS_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EVS-P1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>EVS passage question 1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EVS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EVS_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EVS-P1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>EVS passage question 2</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EVS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EVS_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EVS-P1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EVS passage question 3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EVS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EVS_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EVS-P1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>EVS passage question 4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EVS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EVS_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EVS-P1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>EVS passage question 5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LANGUAGE_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>L-P1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LANGUAGE passage question 1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LANGUAGE_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>L-P1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LANGUAGE passage question 2</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LANGUAGE_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>L-P1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LANGUAGE passage question 3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LANGUAGE_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>L-P1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LANGUAGE passage question 4</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LANGUAGE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LANGUAGE_PASSAGE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>L-P1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LANGUAGE passage question 5</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K6"/>
@@ -764,7 +1368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/mock_question_bank_template_v2.xlsx
+++ b/mock_question_bank_template_v2.xlsx
@@ -7,12 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passages" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Passages" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Questions'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,87 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="115" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>MOCK TEST BULK UPLOAD — PASSAGE RULES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1. For EVS_PASSAGE and LANGUAGE_PASSAGE, Local Passage No. is mandatory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2. Exactly 5 question rows must use the same Local Passage No.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3. Question Order must be exactly 1, 2, 3, 4, 5 for each passage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4. The Passages sheet must contain exactly one row for each Local Passage No.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5. Each passage row must contain a Passage Title and the complete Passage text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6. The system generates the permanent Passage ID automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7. Do not split one passage across different local passage numbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8. Language supports multiple complete 5-question passage groups.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -538,7 +457,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Local Passage No. (required for passage parts)</t>
+          <t>Local Passage No. (optional)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -593,6 +512,7 @@
           <t>EVS_MCQ</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>1</t>
@@ -628,6 +548,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -680,6 +601,7 @@
           <t>B</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -732,6 +654,7 @@
           <t>A</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -784,6 +707,7 @@
           <t>C</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -796,6 +720,7 @@
           <t>ARITHMETIC</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
@@ -831,536 +756,7 @@
           <t>D</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EVS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EVS_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>EVS-P1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>EVS passage question 1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EVS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>EVS_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>EVS-P1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>EVS passage question 2</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EVS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EVS_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>EVS-P1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>EVS passage question 3</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EVS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EVS_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>EVS-P1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>EVS passage question 4</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>EVS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EVS_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>EVS-P1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>EVS passage question 5</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LANGUAGE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LANGUAGE_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>L-P1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LANGUAGE passage question 1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LANGUAGE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>LANGUAGE_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>L-P1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LANGUAGE passage question 2</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LANGUAGE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LANGUAGE_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>L-P1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LANGUAGE passage question 3</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LANGUAGE</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LANGUAGE_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>L-P1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>LANGUAGE passage question 4</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LANGUAGE</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LANGUAGE_PASSAGE</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>L-P1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LANGUAGE passage question 5</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Option B</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K6"/>
@@ -1368,7 +764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
